--- a/vending_machine_refactor/data/vending_machine_from_legacy.xlsx
+++ b/vending_machine_refactor/data/vending_machine_from_legacy.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>images/P001.jpg</t>
+          <t>images/water.jpg</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -547,7 +547,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>images/P002.jpg</t>
+          <t>images/coffee_cup.jpg</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -581,7 +581,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>images/P003.jpg</t>
+          <t>images/ion_drink.jpg</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -615,7 +615,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>images/P004.jpg</t>
+          <t>images/letsbe.jpg</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -649,7 +649,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>images/P005.jpg</t>
+          <t>images/cider.jpg</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -683,7 +683,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>images/P006.jpg</t>
+          <t>images/special_drink.jpg</t>
         </is>
       </c>
       <c r="H7" t="n">
